--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.99123417106523</v>
+        <v>3.2485755527981</v>
       </c>
       <c r="D2" t="n">
-        <v>25.48063953828113</v>
+        <v>4.140603924970684</v>
       </c>
       <c r="E2" t="n">
-        <v>3.73712021720248</v>
+        <v>0.6072820352954029</v>
       </c>
       <c r="F2" t="n">
-        <v>5.878523876815524</v>
+        <v>0.9552601299825225</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.0697544514704</v>
+        <v>1.63633509836394</v>
       </c>
       <c r="D3" t="n">
-        <v>9.200241920199813</v>
+        <v>1.49503931203247</v>
       </c>
       <c r="E3" t="n">
-        <v>3.73712021720248</v>
+        <v>0.6072820352954029</v>
       </c>
       <c r="F3" t="n">
-        <v>5.878523876815524</v>
+        <v>0.9552601299825225</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.71018324879579</v>
+        <v>2.390404777929315</v>
       </c>
       <c r="D4" t="n">
-        <v>14.58313671324201</v>
+        <v>2.369759715901827</v>
       </c>
       <c r="E4" t="n">
-        <v>3.73712021720248</v>
+        <v>0.6072820352954029</v>
       </c>
       <c r="F4" t="n">
-        <v>5.878523876815524</v>
+        <v>0.9552601299825225</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>10.75559421504585</v>
+        <v>1.74778405994495</v>
       </c>
       <c r="D5" t="n">
-        <v>18.75675232437514</v>
+        <v>3.047972252710959</v>
       </c>
       <c r="E5" t="n">
-        <v>3.73712021720248</v>
+        <v>0.6072820352954029</v>
       </c>
       <c r="F5" t="n">
-        <v>5.878523876815524</v>
+        <v>0.9552601299825225</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>10.81695681350421</v>
+        <v>1.757755482194434</v>
       </c>
       <c r="D6" t="n">
-        <v>10.77016628616049</v>
+        <v>1.750152021501079</v>
       </c>
       <c r="E6" t="n">
-        <v>3.73712021720248</v>
+        <v>0.6072820352954029</v>
       </c>
       <c r="F6" t="n">
-        <v>5.878523876815524</v>
+        <v>0.9552601299825225</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
